--- a/artfynd/A 63059-2025 artfynd.xlsx
+++ b/artfynd/A 63059-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ15"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,50 +680,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>136284272</v>
+        <v>136294807</v>
       </c>
       <c r="B2" t="n">
-        <v>57980</v>
+        <v>92073</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Vargmossen, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>669696</v>
+        <v>669758</v>
       </c>
       <c r="R2" t="n">
-        <v>6644199</v>
+        <v>6644186</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,94 +755,87 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>17:01</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>17:01</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Annika Leers</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Annika Leers</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136284272</t>
+          <t>https://artportalen.se/Sighting/136294807</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136284275</v>
+        <v>136294782</v>
       </c>
       <c r="B3" t="n">
-        <v>57980</v>
+        <v>92505</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Vargmossen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>669666</v>
+        <v>669688</v>
       </c>
       <c r="R3" t="n">
-        <v>6644195</v>
+        <v>6644229</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,54 +865,45 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>16:45</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>16:45</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Annika Leers</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Annika Leers, Ki Mähler</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136284275</t>
+          <t>https://artportalen.se/Sighting/136294782</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136284265</v>
+        <v>136295668</v>
       </c>
       <c r="B4" t="n">
-        <v>45276</v>
+        <v>92747</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,34 +911,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102920</v>
+        <v>1339</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grön mosaikslända</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Aeshna viridis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Eversmann, 1836</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Eknäs, Upl</t>
+          <t>Vargmossen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>669729</v>
+        <v>669679</v>
       </c>
       <c r="R4" t="n">
-        <v>6644205</v>
+        <v>6644188</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,86 +975,73 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>17:28</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>17:28</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Annika Leers</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Annika Leers</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136284265</t>
+          <t>https://artportalen.se/Sighting/136295668</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136284253</v>
+        <v>136284272</v>
       </c>
       <c r="B5" t="n">
-        <v>99296</v>
+        <v>57984</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1070,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>669676</v>
+        <v>669696</v>
       </c>
       <c r="R5" t="n">
-        <v>6644223</v>
+        <v>6644199</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1095,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,48 +1121,44 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136284253</t>
+          <t>https://artportalen.se/Sighting/136284272</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136284254</v>
+        <v>136284275</v>
       </c>
       <c r="B6" t="n">
-        <v>99296</v>
+        <v>57984</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1191,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>669670</v>
+        <v>669666</v>
       </c>
       <c r="R6" t="n">
-        <v>6644208</v>
+        <v>6644195</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1226,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1236,7 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,60 +1238,51 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136284254</t>
+          <t>https://artportalen.se/Sighting/136284275</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136284260</v>
+        <v>136284265</v>
       </c>
       <c r="B7" t="n">
-        <v>99296</v>
+        <v>45276</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>102920</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön mosaikslända</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Aeshna viridis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Eversmann, 1836</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Eknäs, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>669740</v>
+        <v>669729</v>
       </c>
       <c r="R7" t="n">
-        <v>6644165</v>
+        <v>6644205</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1357,7 +1324,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1383,16 +1350,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136284260</t>
+          <t>https://artportalen.se/Sighting/136284265</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136284262</v>
+        <v>136284253</v>
       </c>
       <c r="B8" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1419,7 +1386,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1429,14 +1396,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Eknäs, Upl</t>
+          <t>Vargmossen, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>669737</v>
+        <v>669676</v>
       </c>
       <c r="R8" t="n">
-        <v>6644178</v>
+        <v>6644223</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1468,7 +1435,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1478,7 +1445,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1504,16 +1471,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136284262</t>
+          <t>https://artportalen.se/Sighting/136284253</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136284267</v>
+        <v>136284254</v>
       </c>
       <c r="B9" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1507,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1550,14 +1517,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Eknäs, Upl</t>
+          <t>Vargmossen, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>669718</v>
+        <v>669670</v>
       </c>
       <c r="R9" t="n">
-        <v>6644192</v>
+        <v>6644208</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1589,7 +1556,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1599,7 +1566,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1625,16 +1592,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136284267</t>
+          <t>https://artportalen.se/Sighting/136284254</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136284268</v>
+        <v>136284260</v>
       </c>
       <c r="B10" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1628,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1675,10 +1642,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>669724</v>
+        <v>669740</v>
       </c>
       <c r="R10" t="n">
-        <v>6644189</v>
+        <v>6644165</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1710,7 +1677,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1720,7 +1687,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1746,16 +1713,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136284268</t>
+          <t>https://artportalen.se/Sighting/136284260</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136284270</v>
+        <v>136284262</v>
       </c>
       <c r="B11" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1782,7 +1749,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1792,14 +1759,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vargmossen, Upl</t>
+          <t>Eknäs, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>669701</v>
+        <v>669737</v>
       </c>
       <c r="R11" t="n">
-        <v>6644197</v>
+        <v>6644178</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1831,7 +1798,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1841,7 +1808,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1867,16 +1834,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136284270</t>
+          <t>https://artportalen.se/Sighting/136284262</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136284271</v>
+        <v>136284267</v>
       </c>
       <c r="B12" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1903,7 +1870,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1913,14 +1880,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vargmossen, Upl</t>
+          <t>Eknäs, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>669704</v>
+        <v>669718</v>
       </c>
       <c r="R12" t="n">
-        <v>6644196</v>
+        <v>6644192</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1952,7 +1919,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1962,7 +1929,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1988,16 +1955,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136284271</t>
+          <t>https://artportalen.se/Sighting/136284267</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136284273</v>
+        <v>136284268</v>
       </c>
       <c r="B13" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2024,7 +1991,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2034,14 +2001,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vargmossen, Upl</t>
+          <t>Eknäs, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>669702</v>
+        <v>669724</v>
       </c>
       <c r="R13" t="n">
-        <v>6644194</v>
+        <v>6644189</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2073,7 +2040,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2083,7 +2050,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2109,16 +2076,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136284273</t>
+          <t>https://artportalen.se/Sighting/136284268</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136284274</v>
+        <v>136284270</v>
       </c>
       <c r="B14" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2145,7 +2112,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2159,10 +2126,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>669689</v>
+        <v>669701</v>
       </c>
       <c r="R14" t="n">
-        <v>6644207</v>
+        <v>6644197</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2194,7 +2161,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2204,7 +2171,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2230,51 +2197,60 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136284274</t>
+          <t>https://artportalen.se/Sighting/136284270</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136284256</v>
+        <v>136284271</v>
       </c>
       <c r="B15" t="n">
-        <v>99102</v>
+        <v>99302</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>223049</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Eknäs, Upl</t>
+          <t>Vargmossen, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
         <v>669704</v>
       </c>
       <c r="R15" t="n">
-        <v>6644151</v>
+        <v>6644196</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2306,7 +2282,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2316,7 +2292,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2341,6 +2317,1240 @@
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136284271</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136284273</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99302</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Vargmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>669702</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6644194</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Ki Mähler</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Ki Mähler</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136284273</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136284274</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99302</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Vargmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>669689</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6644207</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Ki Mähler</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Ki Mähler</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136284274</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136295749</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99302</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Vargmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>669736</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6644199</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Annika Leers</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Annika Leers</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136295749</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136295830</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99302</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Vargmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>669730</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6644185</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Annika Leers</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Annika Leers</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136295830</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136295888</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99302</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Vargmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>669745</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6644166</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Annika Leers</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Annika Leers</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136295888</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>136296170</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99302</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Vargmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>669748</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6644108</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Annika Leers</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Annika Leers, Ki Mähler</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136296170</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>136296499</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99302</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Vargmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>669659</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6644192</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Annika Leers</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Annika Leers</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136296499</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>136294881</v>
+      </c>
+      <c r="B23" t="n">
+        <v>106443</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Vargmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>669732</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6644108</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Annika Leers</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Annika Leers</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136294881</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>136295698</v>
+      </c>
+      <c r="B24" t="n">
+        <v>106443</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Vargmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>669694</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6644183</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Annika Leers</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Annika Leers, Ki Mähler</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136295698</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>136295567</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98164</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Vargmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>669695</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6644146</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Annika Leers</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Annika Leers</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136295567</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>136284256</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99108</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Eknäs, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>669704</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6644151</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Ki Mähler</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Ki Mähler</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136284256</t>
         </is>
@@ -2362,6 +3572,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 63059-2025 artfynd.xlsx
+++ b/artfynd/A 63059-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136294807</v>
       </c>
       <c r="B2" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136294782</v>
       </c>
       <c r="B3" t="n">
-        <v>92505</v>
+        <v>92506</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136295668</v>
       </c>
       <c r="B4" t="n">
-        <v>92747</v>
+        <v>92748</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136284272</v>
       </c>
       <c r="B5" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>136284275</v>
       </c>
       <c r="B6" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136284253</v>
       </c>
       <c r="B8" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>136284254</v>
       </c>
       <c r="B9" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136284260</v>
       </c>
       <c r="B10" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>136284262</v>
       </c>
       <c r="B11" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>136284267</v>
       </c>
       <c r="B12" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>136284268</v>
       </c>
       <c r="B13" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>136284270</v>
       </c>
       <c r="B14" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>136284271</v>
       </c>
       <c r="B15" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>136284273</v>
       </c>
       <c r="B16" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>136284274</v>
       </c>
       <c r="B17" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>136295749</v>
       </c>
       <c r="B18" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         <v>136295830</v>
       </c>
       <c r="B19" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>136295888</v>
       </c>
       <c r="B20" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>136296170</v>
       </c>
       <c r="B21" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>136296499</v>
       </c>
       <c r="B22" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>136294881</v>
       </c>
       <c r="B23" t="n">
-        <v>106443</v>
+        <v>106444</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>136295698</v>
       </c>
       <c r="B24" t="n">
-        <v>106443</v>
+        <v>106444</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>136295567</v>
       </c>
       <c r="B25" t="n">
-        <v>98164</v>
+        <v>98165</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>136284256</v>
       </c>
       <c r="B26" t="n">
-        <v>99108</v>
+        <v>99109</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 63059-2025 artfynd.xlsx
+++ b/artfynd/A 63059-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136294807</v>
       </c>
       <c r="B2" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136294782</v>
       </c>
       <c r="B3" t="n">
-        <v>92506</v>
+        <v>92512</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136295668</v>
       </c>
       <c r="B4" t="n">
-        <v>92748</v>
+        <v>92754</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136284253</v>
       </c>
       <c r="B8" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>136284254</v>
       </c>
       <c r="B9" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136284260</v>
       </c>
       <c r="B10" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>136284262</v>
       </c>
       <c r="B11" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>136284267</v>
       </c>
       <c r="B12" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>136284268</v>
       </c>
       <c r="B13" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>136284270</v>
       </c>
       <c r="B14" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>136284271</v>
       </c>
       <c r="B15" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>136284273</v>
       </c>
       <c r="B16" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>136284274</v>
       </c>
       <c r="B17" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>136295749</v>
       </c>
       <c r="B18" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         <v>136295830</v>
       </c>
       <c r="B19" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>136295888</v>
       </c>
       <c r="B20" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>136296170</v>
       </c>
       <c r="B21" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>136296499</v>
       </c>
       <c r="B22" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>136294881</v>
       </c>
       <c r="B23" t="n">
-        <v>106444</v>
+        <v>106455</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>136295698</v>
       </c>
       <c r="B24" t="n">
-        <v>106444</v>
+        <v>106455</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>136295567</v>
       </c>
       <c r="B25" t="n">
-        <v>98165</v>
+        <v>98176</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>136284256</v>
       </c>
       <c r="B26" t="n">
-        <v>99109</v>
+        <v>99120</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 63059-2025 artfynd.xlsx
+++ b/artfynd/A 63059-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136294807</v>
       </c>
       <c r="B2" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136294782</v>
       </c>
       <c r="B3" t="n">
-        <v>92512</v>
+        <v>92519</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136295668</v>
       </c>
       <c r="B4" t="n">
-        <v>92754</v>
+        <v>92761</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136284272</v>
       </c>
       <c r="B5" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>136284275</v>
       </c>
       <c r="B6" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>136284265</v>
       </c>
       <c r="B7" t="n">
-        <v>45276</v>
+        <v>45281</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136284253</v>
       </c>
       <c r="B8" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>136284254</v>
       </c>
       <c r="B9" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136284260</v>
       </c>
       <c r="B10" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>136284262</v>
       </c>
       <c r="B11" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>136284267</v>
       </c>
       <c r="B12" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>136284268</v>
       </c>
       <c r="B13" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>136284270</v>
       </c>
       <c r="B14" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>136284271</v>
       </c>
       <c r="B15" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>136284273</v>
       </c>
       <c r="B16" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>136284274</v>
       </c>
       <c r="B17" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>136295749</v>
       </c>
       <c r="B18" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         <v>136295830</v>
       </c>
       <c r="B19" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>136295888</v>
       </c>
       <c r="B20" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>136296170</v>
       </c>
       <c r="B21" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>136296499</v>
       </c>
       <c r="B22" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>136294881</v>
       </c>
       <c r="B23" t="n">
-        <v>106455</v>
+        <v>106468</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>136295698</v>
       </c>
       <c r="B24" t="n">
-        <v>106455</v>
+        <v>106468</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>136295567</v>
       </c>
       <c r="B25" t="n">
-        <v>98176</v>
+        <v>98189</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>136284256</v>
       </c>
       <c r="B26" t="n">
-        <v>99120</v>
+        <v>99133</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 63059-2025 artfynd.xlsx
+++ b/artfynd/A 63059-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ26"/>
+  <dimension ref="A1:AZ41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1010,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136284272</v>
+        <v>136423298</v>
       </c>
       <c r="B5" t="n">
-        <v>57990</v>
+        <v>92761</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,42 +1021,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Vargmossen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>669696</v>
+        <v>669893</v>
       </c>
       <c r="R5" t="n">
-        <v>6644199</v>
+        <v>6644082</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,22 +1075,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1110,27 +1105,27 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Annika Leers</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Annika Leers</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136284272</t>
+          <t>https://artportalen.se/Sighting/136423298</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136284275</v>
+        <v>136423296</v>
       </c>
       <c r="B6" t="n">
-        <v>57990</v>
+        <v>92050</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,42 +1133,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Vargmossen, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>669666</v>
+        <v>669719</v>
       </c>
       <c r="R6" t="n">
-        <v>6644195</v>
+        <v>6644130</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1197,22 +1187,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Kanske?</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1227,27 +1222,27 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Annika Leers</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Annika Leers</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136284275</t>
+          <t>https://artportalen.se/Sighting/136423296</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136284265</v>
+        <v>136284272</v>
       </c>
       <c r="B7" t="n">
-        <v>45281</v>
+        <v>57990</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1255,34 +1250,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102920</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grön mosaikslända</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Aeshna viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Eversmann, 1836</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Eknäs, Upl</t>
+          <t>Vargmossen, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>669729</v>
+        <v>669696</v>
       </c>
       <c r="R7" t="n">
-        <v>6644205</v>
+        <v>6644199</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,48 +1350,44 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136284265</t>
+          <t>https://artportalen.se/Sighting/136284272</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136284253</v>
+        <v>136284275</v>
       </c>
       <c r="B8" t="n">
-        <v>99327</v>
+        <v>57990</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1400,10 +1396,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>669676</v>
+        <v>669666</v>
       </c>
       <c r="R8" t="n">
-        <v>6644223</v>
+        <v>6644195</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1435,7 +1431,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1445,7 +1441,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,63 +1467,62 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136284253</t>
+          <t>https://artportalen.se/Sighting/136284275</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136284254</v>
+        <v>136423289</v>
       </c>
       <c r="B9" t="n">
-        <v>99327</v>
+        <v>57990</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Vargmossen, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>669670</v>
+        <v>669415</v>
       </c>
       <c r="R9" t="n">
-        <v>6644208</v>
+        <v>6644167</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1551,22 +1546,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,74 +1576,73 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Annika Leers</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Annika Leers</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136284254</t>
+          <t>https://artportalen.se/Sighting/136423289</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136284260</v>
+        <v>136423300</v>
       </c>
       <c r="B10" t="n">
-        <v>99327</v>
+        <v>57990</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Eknäs, Upl</t>
+          <t>Vargmossen, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>669740</v>
+        <v>669900</v>
       </c>
       <c r="R10" t="n">
-        <v>6644165</v>
+        <v>6644161</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1672,22 +1666,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,71 +1696,62 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Annika Leers</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Annika Leers</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136284260</t>
+          <t>https://artportalen.se/Sighting/136423300</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136284262</v>
+        <v>136423424</v>
       </c>
       <c r="B11" t="n">
-        <v>99327</v>
+        <v>4783</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Eknäs, Upl</t>
+          <t>Vargmossen, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>669737</v>
+        <v>669527</v>
       </c>
       <c r="R11" t="n">
-        <v>6644178</v>
+        <v>6644205</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1793,22 +1778,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1834,60 +1819,51 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136284262</t>
+          <t>https://artportalen.se/Sighting/136423424</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136284267</v>
+        <v>136284265</v>
       </c>
       <c r="B12" t="n">
-        <v>99327</v>
+        <v>45281</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>102920</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön mosaikslända</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Aeshna viridis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Eversmann, 1836</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Eknäs, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>669718</v>
+        <v>669729</v>
       </c>
       <c r="R12" t="n">
-        <v>6644192</v>
+        <v>6644205</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1919,7 +1895,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1929,7 +1905,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1955,13 +1931,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136284267</t>
+          <t>https://artportalen.se/Sighting/136284265</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136284268</v>
+        <v>136284253</v>
       </c>
       <c r="B13" t="n">
         <v>99327</v>
@@ -1991,7 +1967,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2001,14 +1977,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Eknäs, Upl</t>
+          <t>Vargmossen, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>669724</v>
+        <v>669676</v>
       </c>
       <c r="R13" t="n">
-        <v>6644189</v>
+        <v>6644223</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2040,7 +2016,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2050,7 +2026,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2076,13 +2052,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136284268</t>
+          <t>https://artportalen.se/Sighting/136284253</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136284270</v>
+        <v>136284254</v>
       </c>
       <c r="B14" t="n">
         <v>99327</v>
@@ -2112,7 +2088,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2126,10 +2102,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>669701</v>
+        <v>669670</v>
       </c>
       <c r="R14" t="n">
-        <v>6644197</v>
+        <v>6644208</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2161,7 +2137,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2171,7 +2147,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2197,13 +2173,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136284270</t>
+          <t>https://artportalen.se/Sighting/136284254</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136284271</v>
+        <v>136284260</v>
       </c>
       <c r="B15" t="n">
         <v>99327</v>
@@ -2233,7 +2209,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2243,14 +2219,14 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vargmossen, Upl</t>
+          <t>Eknäs, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>669704</v>
+        <v>669740</v>
       </c>
       <c r="R15" t="n">
-        <v>6644196</v>
+        <v>6644165</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2282,7 +2258,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2292,7 +2268,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2318,13 +2294,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136284271</t>
+          <t>https://artportalen.se/Sighting/136284260</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136284273</v>
+        <v>136284262</v>
       </c>
       <c r="B16" t="n">
         <v>99327</v>
@@ -2354,7 +2330,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2364,14 +2340,14 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Vargmossen, Upl</t>
+          <t>Eknäs, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>669702</v>
+        <v>669737</v>
       </c>
       <c r="R16" t="n">
-        <v>6644194</v>
+        <v>6644178</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2403,7 +2379,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2413,7 +2389,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2439,13 +2415,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136284273</t>
+          <t>https://artportalen.se/Sighting/136284262</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>136284274</v>
+        <v>136284267</v>
       </c>
       <c r="B17" t="n">
         <v>99327</v>
@@ -2475,7 +2451,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2485,14 +2461,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vargmossen, Upl</t>
+          <t>Eknäs, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>669689</v>
+        <v>669718</v>
       </c>
       <c r="R17" t="n">
-        <v>6644207</v>
+        <v>6644192</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2524,7 +2500,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2534,7 +2510,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2560,13 +2536,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136284274</t>
+          <t>https://artportalen.se/Sighting/136284267</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>136295749</v>
+        <v>136284268</v>
       </c>
       <c r="B18" t="n">
         <v>99327</v>
@@ -2599,20 +2575,21 @@
           <t>13</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Vargmossen, Upl</t>
+          <t>Eknäs, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>669736</v>
+        <v>669724</v>
       </c>
       <c r="R18" t="n">
-        <v>6644199</v>
+        <v>6644189</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2642,42 +2619,51 @@
           <t>2026-09-01</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Annika Leers</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Annika Leers</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136295749</t>
+          <t>https://artportalen.se/Sighting/136284268</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136295830</v>
+        <v>136284270</v>
       </c>
       <c r="B19" t="n">
         <v>99327</v>
@@ -2707,23 +2693,24 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Vargmossen, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>669730</v>
+        <v>669701</v>
       </c>
       <c r="R19" t="n">
-        <v>6644185</v>
+        <v>6644197</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2753,42 +2740,51 @@
           <t>2026-09-01</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Annika Leers</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Annika Leers</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136295830</t>
+          <t>https://artportalen.se/Sighting/136284270</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>136295888</v>
+        <v>136284271</v>
       </c>
       <c r="B20" t="n">
         <v>99327</v>
@@ -2818,23 +2814,24 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Vargmossen, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>669745</v>
+        <v>669704</v>
       </c>
       <c r="R20" t="n">
-        <v>6644166</v>
+        <v>6644196</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2864,42 +2861,51 @@
           <t>2026-09-01</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Annika Leers</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Annika Leers</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136295888</t>
+          <t>https://artportalen.se/Sighting/136284271</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>136296170</v>
+        <v>136284273</v>
       </c>
       <c r="B21" t="n">
         <v>99327</v>
@@ -2929,23 +2935,24 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Vargmossen, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>669748</v>
+        <v>669702</v>
       </c>
       <c r="R21" t="n">
-        <v>6644108</v>
+        <v>6644194</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2975,42 +2982,51 @@
           <t>2026-09-01</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Annika Leers</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Annika Leers, Ki Mähler</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136296170</t>
+          <t>https://artportalen.se/Sighting/136284273</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>136296499</v>
+        <v>136284274</v>
       </c>
       <c r="B22" t="n">
         <v>99327</v>
@@ -3040,23 +3056,24 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Vargmossen, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>669659</v>
+        <v>669689</v>
       </c>
       <c r="R22" t="n">
-        <v>6644192</v>
+        <v>6644207</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3086,72 +3103,81 @@
           <t>2026-09-01</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Annika Leers</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Annika Leers</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136296499</t>
+          <t>https://artportalen.se/Sighting/136284274</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>136294881</v>
+        <v>136295749</v>
       </c>
       <c r="B23" t="n">
-        <v>106468</v>
+        <v>99327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
@@ -3164,10 +3190,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>669732</v>
+        <v>669736</v>
       </c>
       <c r="R23" t="n">
-        <v>6644108</v>
+        <v>6644199</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3226,41 +3252,45 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136294881</t>
+          <t>https://artportalen.se/Sighting/136295749</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>136295698</v>
+        <v>136295830</v>
       </c>
       <c r="B24" t="n">
-        <v>106468</v>
+        <v>99327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
@@ -3271,10 +3301,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>669694</v>
+        <v>669730</v>
       </c>
       <c r="R24" t="n">
-        <v>6644183</v>
+        <v>6644185</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3327,47 +3357,51 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Annika Leers, Ki Mähler</t>
+          <t>Annika Leers</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136295698</t>
+          <t>https://artportalen.se/Sighting/136295830</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>136295567</v>
+        <v>136295888</v>
       </c>
       <c r="B25" t="n">
-        <v>98189</v>
+        <v>99327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
@@ -3378,10 +3412,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>669695</v>
+        <v>669745</v>
       </c>
       <c r="R25" t="n">
-        <v>6644146</v>
+        <v>6644166</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3440,51 +3474,59 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136295567</t>
+          <t>https://artportalen.se/Sighting/136295888</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>136284256</v>
+        <v>136296170</v>
       </c>
       <c r="B26" t="n">
-        <v>99133</v>
+        <v>99327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>223049</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Eknäs, Upl</t>
+          <t>Vargmossen, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>669704</v>
+        <v>669748</v>
       </c>
       <c r="R26" t="n">
-        <v>6644151</v>
+        <v>6644108</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3514,43 +3556,1760 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>18:05</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>18:05</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Annika Leers</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Annika Leers, Ki Mähler</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136296170</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>136296499</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99327</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Vargmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>669659</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6644192</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Annika Leers</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Annika Leers</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136296499</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>136423302</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99327</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Vargmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>669760</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6644126</v>
+      </c>
+      <c r="S28" t="n">
+        <v>11</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Annika Leers</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Annika Leers</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136423302</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>136423405</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99327</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Eknäs, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>669766</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6644105</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Ki Mähler</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Ki Mähler</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136423405</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>136423413</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99327</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Eknäs, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>669838</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6644030</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Ki Mähler</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Ki Mähler</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136423413</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>136423414</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99327</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Eknäs, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>669828</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6644050</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Ki Mähler</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Ki Mähler</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136423414</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>136423415</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99327</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Eknäs, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>669826</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6644050</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Ki Mähler</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Ki Mähler</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136423415</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>136423418</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99327</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Eknäs, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>669722</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6644125</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Ki Mähler</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Ki Mähler</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136423418</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>136423419</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99327</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Vargmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>669553</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6644181</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Ki Mähler</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Ki Mähler</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136423419</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>136294881</v>
+      </c>
+      <c r="B35" t="n">
+        <v>106468</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Vargmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>669732</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6644108</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Annika Leers</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Annika Leers</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136294881</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>136295698</v>
+      </c>
+      <c r="B36" t="n">
+        <v>106468</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Vargmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>669694</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6644183</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Annika Leers</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Annika Leers, Ki Mähler</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136295698</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>136295567</v>
+      </c>
+      <c r="B37" t="n">
+        <v>98189</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Vargmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>669695</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6644146</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Annika Leers</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Annika Leers</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136295567</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>136423286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>101537</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Vargmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>669530</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6644233</v>
+      </c>
+      <c r="S38" t="n">
+        <v>13</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Annika Leers</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Annika Leers</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136423286</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>136423288</v>
+      </c>
+      <c r="B39" t="n">
+        <v>101537</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Vargmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>669382</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6644141</v>
+      </c>
+      <c r="S39" t="n">
+        <v>8</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Annika Leers</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Annika Leers</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136423288</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>136423295</v>
+      </c>
+      <c r="B40" t="n">
+        <v>101537</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Vargmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>669592</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6644217</v>
+      </c>
+      <c r="S40" t="n">
+        <v>11</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Annika Leers</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Annika Leers</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136423295</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>136284256</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99133</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Eknäs, Upl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>669704</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6644151</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Ki Mähler</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Ki Mähler</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136284256</t>
         </is>
@@ -3583,6 +5342,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 63059-2025 artfynd.xlsx
+++ b/artfynd/A 63059-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136294807</v>
       </c>
       <c r="B2" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136294782</v>
       </c>
       <c r="B3" t="n">
-        <v>92519</v>
+        <v>92520</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136295668</v>
       </c>
       <c r="B4" t="n">
-        <v>92761</v>
+        <v>92762</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136423298</v>
       </c>
       <c r="B5" t="n">
-        <v>92761</v>
+        <v>92762</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>136423296</v>
       </c>
       <c r="B6" t="n">
-        <v>92050</v>
+        <v>92051</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>136284253</v>
       </c>
       <c r="B13" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136284254</v>
       </c>
       <c r="B14" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>136284260</v>
       </c>
       <c r="B15" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>136284262</v>
       </c>
       <c r="B16" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>136284267</v>
       </c>
       <c r="B17" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>136284268</v>
       </c>
       <c r="B18" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>136284270</v>
       </c>
       <c r="B19" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>136284271</v>
       </c>
       <c r="B20" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>136284273</v>
       </c>
       <c r="B21" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>136284274</v>
       </c>
       <c r="B22" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>136295749</v>
       </c>
       <c r="B23" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
         <v>136295830</v>
       </c>
       <c r="B24" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>136295888</v>
       </c>
       <c r="B25" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>136296170</v>
       </c>
       <c r="B26" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         <v>136296499</v>
       </c>
       <c r="B27" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>136423302</v>
       </c>
       <c r="B28" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>136423405</v>
       </c>
       <c r="B29" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>136423413</v>
       </c>
       <c r="B30" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>136423414</v>
       </c>
       <c r="B31" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>136423415</v>
       </c>
       <c r="B32" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>136423418</v>
       </c>
       <c r="B33" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>136423419</v>
       </c>
       <c r="B34" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         <v>136294881</v>
       </c>
       <c r="B35" t="n">
-        <v>106468</v>
+        <v>106469</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>136295698</v>
       </c>
       <c r="B36" t="n">
-        <v>106468</v>
+        <v>106469</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>136295567</v>
       </c>
       <c r="B37" t="n">
-        <v>98189</v>
+        <v>98190</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4872,7 +4872,7 @@
         <v>136423286</v>
       </c>
       <c r="B38" t="n">
-        <v>101537</v>
+        <v>101538</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>136423288</v>
       </c>
       <c r="B39" t="n">
-        <v>101537</v>
+        <v>101538</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
         <v>136423295</v>
       </c>
       <c r="B40" t="n">
-        <v>101537</v>
+        <v>101538</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>136284256</v>
       </c>
       <c r="B41" t="n">
-        <v>99133</v>
+        <v>99134</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 63059-2025 artfynd.xlsx
+++ b/artfynd/A 63059-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136294807</v>
       </c>
       <c r="B2" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136294782</v>
       </c>
       <c r="B3" t="n">
-        <v>92520</v>
+        <v>92533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136295668</v>
       </c>
       <c r="B4" t="n">
-        <v>92762</v>
+        <v>92775</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136423298</v>
       </c>
       <c r="B5" t="n">
-        <v>92762</v>
+        <v>92775</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>136423296</v>
       </c>
       <c r="B6" t="n">
-        <v>92051</v>
+        <v>92064</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>136284272</v>
       </c>
       <c r="B7" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136284275</v>
       </c>
       <c r="B8" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>136423289</v>
       </c>
       <c r="B9" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>136423300</v>
       </c>
       <c r="B10" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>136284265</v>
       </c>
       <c r="B12" t="n">
-        <v>45281</v>
+        <v>45294</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>136284253</v>
       </c>
       <c r="B13" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136284254</v>
       </c>
       <c r="B14" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>136284260</v>
       </c>
       <c r="B15" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>136284262</v>
       </c>
       <c r="B16" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>136284267</v>
       </c>
       <c r="B17" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>136284268</v>
       </c>
       <c r="B18" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>136284270</v>
       </c>
       <c r="B19" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>136284271</v>
       </c>
       <c r="B20" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>136284273</v>
       </c>
       <c r="B21" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>136284274</v>
       </c>
       <c r="B22" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>136295749</v>
       </c>
       <c r="B23" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
         <v>136295830</v>
       </c>
       <c r="B24" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>136295888</v>
       </c>
       <c r="B25" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>136296170</v>
       </c>
       <c r="B26" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         <v>136296499</v>
       </c>
       <c r="B27" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>136423302</v>
       </c>
       <c r="B28" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>136423405</v>
       </c>
       <c r="B29" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>136423413</v>
       </c>
       <c r="B30" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>136423414</v>
       </c>
       <c r="B31" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>136423415</v>
       </c>
       <c r="B32" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>136423418</v>
       </c>
       <c r="B33" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>136423419</v>
       </c>
       <c r="B34" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         <v>136294881</v>
       </c>
       <c r="B35" t="n">
-        <v>106469</v>
+        <v>106482</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>136295698</v>
       </c>
       <c r="B36" t="n">
-        <v>106469</v>
+        <v>106482</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>136295567</v>
       </c>
       <c r="B37" t="n">
-        <v>98190</v>
+        <v>98203</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4872,7 +4872,7 @@
         <v>136423286</v>
       </c>
       <c r="B38" t="n">
-        <v>101538</v>
+        <v>101551</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>136423288</v>
       </c>
       <c r="B39" t="n">
-        <v>101538</v>
+        <v>101551</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
         <v>136423295</v>
       </c>
       <c r="B40" t="n">
-        <v>101538</v>
+        <v>101551</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>136284256</v>
       </c>
       <c r="B41" t="n">
-        <v>99134</v>
+        <v>99147</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 63059-2025 artfynd.xlsx
+++ b/artfynd/A 63059-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136294807</v>
       </c>
       <c r="B2" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136294782</v>
       </c>
       <c r="B3" t="n">
-        <v>92533</v>
+        <v>92534</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136295668</v>
       </c>
       <c r="B4" t="n">
-        <v>92775</v>
+        <v>92776</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136423298</v>
       </c>
       <c r="B5" t="n">
-        <v>92775</v>
+        <v>92776</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>136423296</v>
       </c>
       <c r="B6" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>136284253</v>
       </c>
       <c r="B13" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136284254</v>
       </c>
       <c r="B14" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>136284260</v>
       </c>
       <c r="B15" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>136284262</v>
       </c>
       <c r="B16" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>136284267</v>
       </c>
       <c r="B17" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>136284268</v>
       </c>
       <c r="B18" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>136284270</v>
       </c>
       <c r="B19" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>136284271</v>
       </c>
       <c r="B20" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>136284273</v>
       </c>
       <c r="B21" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>136284274</v>
       </c>
       <c r="B22" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>136295749</v>
       </c>
       <c r="B23" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
         <v>136295830</v>
       </c>
       <c r="B24" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>136295888</v>
       </c>
       <c r="B25" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>136296170</v>
       </c>
       <c r="B26" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         <v>136296499</v>
       </c>
       <c r="B27" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>136423302</v>
       </c>
       <c r="B28" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>136423405</v>
       </c>
       <c r="B29" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>136423413</v>
       </c>
       <c r="B30" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>136423414</v>
       </c>
       <c r="B31" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>136423415</v>
       </c>
       <c r="B32" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>136423418</v>
       </c>
       <c r="B33" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>136423419</v>
       </c>
       <c r="B34" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         <v>136294881</v>
       </c>
       <c r="B35" t="n">
-        <v>106482</v>
+        <v>106483</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>136295698</v>
       </c>
       <c r="B36" t="n">
-        <v>106482</v>
+        <v>106483</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>136295567</v>
       </c>
       <c r="B37" t="n">
-        <v>98203</v>
+        <v>98204</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4872,7 +4872,7 @@
         <v>136423286</v>
       </c>
       <c r="B38" t="n">
-        <v>101551</v>
+        <v>101552</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>136423288</v>
       </c>
       <c r="B39" t="n">
-        <v>101551</v>
+        <v>101552</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
         <v>136423295</v>
       </c>
       <c r="B40" t="n">
-        <v>101551</v>
+        <v>101552</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>136284256</v>
       </c>
       <c r="B41" t="n">
-        <v>99147</v>
+        <v>99148</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
